--- a/csv/ccus_q1_2026_中文分析报告.xlsx
+++ b/csv/ccus_q1_2026_中文分析报告.xlsx
@@ -472,6 +472,541 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>各标签月度分布</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$9:$H$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$10:$H$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$11:$H$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$12:$H$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$13:$H$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$14:$H$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$15:$H$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$16:$H$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$17:$H$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$18:$H$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="10"/>
+          <order val="10"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$19:$H$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$20:$H$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$21:$H$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="13"/>
+          <order val="13"/>
+          <tx>
+            <strRef>
+              <f>'月度趋势'!F22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月度趋势'!$F$9:$H$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月度趋势'!$G$22:$H$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>月份</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>提及次数</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -540,6 +1075,28 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1456,7 +2013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1480,6 +2037,11 @@
           <t>前三标签摘要</t>
         </is>
       </c>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1495,6 +2057,11 @@
           <t>碳移除 55 次，碳捕集 40 次，碳封存 18 次</t>
         </is>
       </c>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1510,6 +2077,11 @@
           <t>碳移除 56 次，碳捕集 44 次，碳封存 28 次</t>
         </is>
       </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1524,6 +2096,341 @@
         <is>
           <t>碳移除 58 次，碳捕集 38 次，生物质 15 次</t>
         </is>
+      </c>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>标签月度分布数据</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>碳封存</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>生物质</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>碳市场</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>直接空气捕集</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>矿化</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>政策</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>森林碳汇</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>农业碳汇</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>碳利用</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>生物质能碳捕集与封存</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>海洋碳汇</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/csv/ccus_q1_2026_中文分析报告.xlsx
+++ b/csv/ccus_q1_2026_中文分析报告.xlsx
@@ -485,15 +485,16 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>各标签月度分布</a:t>
+              <a:t>各领域月度分布</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -507,22 +508,14 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
+              <f>'月度趋势'!$E$10:$E$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'月度趋势'!$G$9:$H$9</f>
+              <f>'月度趋势'!$F$10:$F$22</f>
             </numRef>
           </val>
         </ser>
@@ -531,7 +524,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'月度趋势'!F10</f>
+              <f>'月度趋势'!G9</f>
             </strRef>
           </tx>
           <spPr>
@@ -539,22 +532,14 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
+              <f>'月度趋势'!$E$10:$E$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'月度趋势'!$G$10:$H$10</f>
+              <f>'月度趋势'!$G$10:$G$22</f>
             </numRef>
           </val>
         </ser>
@@ -563,7 +548,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'月度趋势'!F11</f>
+              <f>'月度趋势'!H9</f>
             </strRef>
           </tx>
           <spPr>
@@ -571,380 +556,22 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
+              <f>'月度趋势'!$E$10:$E$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'月度趋势'!$G$11:$H$11</f>
+              <f>'月度趋势'!$H$10:$H$22</f>
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'月度趋势'!F12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'月度趋势'!$G$12:$H$12</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'月度趋势'!F13</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'月度趋势'!$G$13:$H$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'月度趋势'!F14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'月度趋势'!$G$14:$H$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'月度趋势'!F15</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'月度趋势'!$G$15:$H$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'月度趋势'!F16</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'月度趋势'!$G$16:$H$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <tx>
-            <strRef>
-              <f>'月度趋势'!F17</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'月度趋势'!$G$17:$H$17</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <tx>
-            <strRef>
-              <f>'月度趋势'!F18</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'月度趋势'!$G$18:$H$18</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="10"/>
-          <order val="10"/>
-          <tx>
-            <strRef>
-              <f>'月度趋势'!F19</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'月度趋势'!$G$19:$H$19</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="11"/>
-          <order val="11"/>
-          <tx>
-            <strRef>
-              <f>'月度趋势'!F20</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'月度趋势'!$G$20:$H$20</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="12"/>
-          <order val="12"/>
-          <tx>
-            <strRef>
-              <f>'月度趋势'!F21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'月度趋势'!$G$21:$H$21</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="13"/>
-          <order val="13"/>
-          <tx>
-            <strRef>
-              <f>'月度趋势'!F22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'月度趋势'!$F$9:$H$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'月度趋势'!$G$22:$H$22</f>
-            </numRef>
-          </val>
-        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
-      </lineChart>
+      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -960,7 +587,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>月份</a:t>
+                  <a:t>提及次数</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -987,7 +614,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>提及次数</a:t>
+                  <a:t>领域</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2013,7 +1640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2042,6 +1669,7 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2062,6 +1690,7 @@
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2082,6 +1711,7 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2102,6 +1732,7 @@
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -2112,6 +1743,7 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -2122,6 +1754,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -2132,6 +1765,7 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -2140,12 +1774,13 @@
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>标签月度分布数据</t>
+          <t>各领域月度分布数据</t>
         </is>
       </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -2154,7 +1789,7 @@
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>标签</t>
+          <t>分类</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -2170,6 +1805,11 @@
       <c r="H9" s="4" t="inlineStr">
         <is>
           <t>2026-03</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Q1合计</t>
         </is>
       </c>
     </row>
@@ -2192,6 +1832,9 @@
       <c r="H10" s="2" t="n">
         <v>58</v>
       </c>
+      <c r="I10" s="2" t="n">
+        <v>169</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -2212,6 +1855,9 @@
       <c r="H11" s="2" t="n">
         <v>38</v>
       </c>
+      <c r="I11" s="2" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -2232,6 +1878,9 @@
       <c r="H12" s="2" t="n">
         <v>14</v>
       </c>
+      <c r="I12" s="2" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -2252,6 +1901,9 @@
       <c r="H13" s="2" t="n">
         <v>15</v>
       </c>
+      <c r="I13" s="2" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -2272,6 +1924,9 @@
       <c r="H14" s="2" t="n">
         <v>12</v>
       </c>
+      <c r="I14" s="2" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -2292,6 +1947,9 @@
       <c r="H15" s="2" t="n">
         <v>10</v>
       </c>
+      <c r="I15" s="2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -2312,6 +1970,9 @@
       <c r="H16" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="I16" s="2" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -2332,6 +1993,9 @@
       <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="I17" s="2" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -2352,6 +2016,9 @@
       <c r="H18" s="2" t="n">
         <v>7</v>
       </c>
+      <c r="I18" s="2" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -2372,6 +2039,9 @@
       <c r="H19" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="I19" s="2" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -2392,6 +2062,9 @@
       <c r="H20" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="I20" s="2" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -2412,6 +2085,9 @@
       <c r="H21" s="2" t="n">
         <v>7</v>
       </c>
+      <c r="I21" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -2431,6 +2107,9 @@
       </c>
       <c r="H22" s="2" t="n">
         <v>3</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/csv/ccus_q1_2026_中文分析报告.xlsx
+++ b/csv/ccus_q1_2026_中文分析报告.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标签统计" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度趋势" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新闻明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四大类统计" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳移除技术" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度趋势" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新闻明细" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -187,7 +188,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>CCUS 各领域新闻提及次数</a:t>
+              <a:t>CCUS 四大类提及次数</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -202,7 +203,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'标签统计'!C1</f>
+              <f>'四大类统计'!C1</f>
             </strRef>
           </tx>
           <spPr>
@@ -212,12 +213,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'标签统计'!$B$2:$B$14</f>
+              <f>'四大类统计'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'标签统计'!$C$2:$C$14</f>
+              <f>'四大类统计'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -270,7 +271,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>领域</a:t>
+                  <a:t>分类</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -300,7 +301,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>CCUS 各领域占比</a:t>
+              <a:t>CCUS 四大类占比</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -314,7 +315,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'标签统计'!C1</f>
+              <f>'四大类统计'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -324,12 +325,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'标签统计'!$B$2:$B$14</f>
+              <f>'四大类统计'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'标签统计'!$C$2:$C$14</f>
+              <f>'四大类统计'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -351,6 +352,182 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>碳移除细分技术提及次数</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'碳移除技术'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'碳移除技术'!$A$2:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'碳移除技术'!$C$2:$C$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>提及次数</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>技术方向</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>碳移除细分技术占比</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'碳移除技术'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'碳移除技术'!$A$2:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'碳移除技术'!$D$2:$D$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showPercent val="1"/>
+          <showLeaderLines val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -472,7 +649,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -485,7 +662,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>各领域月度分布</a:t>
+              <a:t>四大类月度分布</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -510,12 +687,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'月度趋势'!$E$10:$E$22</f>
+              <f>'月度趋势'!$E$10:$E$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'月度趋势'!$F$10:$F$22</f>
+              <f>'月度趋势'!$F$10:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -534,12 +711,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'月度趋势'!$E$10:$E$22</f>
+              <f>'月度趋势'!$E$10:$E$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'月度趋势'!$G$10:$G$22</f>
+              <f>'月度趋势'!$G$10:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -558,12 +735,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'月度趋势'!$E$10:$E$22</f>
+              <f>'月度趋势'!$E$10:$E$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'月度趋势'!$H$10:$H$22</f>
+              <f>'月度趋势'!$H$10:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -614,7 +791,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>领域</a:t>
+                  <a:t>分类</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -684,6 +861,55 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1021,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1069,7 +1295,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>标签统计文件：carbonherald_q1_2026_tag_counts.csv</t>
+          <t>统计区间：2026-01-01 至 2026-03-31</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -1079,7 +1305,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>统计区间：2026-01-01 至 2026-03-31</t>
+          <t>新闻总量：278 篇</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -1089,7 +1315,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>新闻总量：278 篇</t>
+          <t>本次分析仅保留四个大类：碳封存、碳捕集、碳移除、碳利用。</t>
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
@@ -1099,7 +1325,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>纳入统计的标签阈值：不少于 15 次</t>
+          <t>不纳入统计：碳市场、政策及其他非上述四类标签。</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -1109,7 +1335,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>纳入统计的标签提及量：629 次</t>
+          <t>四大类合计提及量：563 次</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -1117,25 +1343,25 @@
       <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>碳移除细分技术合计提及量：190 次</t>
+        </is>
+      </c>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>二、核心结论</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>一季度新闻量总体稳定，1月 92 篇，2月 96 篇，3月 90 篇，峰值出现在 2026-02，低点出现在 2026-03。</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>二、核心结论</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -1145,7 +1371,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>领域关注度高度集中在“碳移除”、“碳捕集”和“碳封存”。三者合计 351 次，占全部标签提及的 55.8%。</t>
+          <t>一季度新闻量总体稳定，1月 92 篇，2月 96 篇，3月 90 篇，峰值出现在 2026-02，低点出现在 2026-03。</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -1155,7 +1381,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>“碳移除”连续三个月保持第一，分别为 55、56、58 次，说明碳移除仍是季度主线。</t>
+          <t>四大类中，“碳移除”以 359 次居首，占四大类提及量的 63.8%；“碳捕集”以 122 次位列第二。</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -1165,7 +1391,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>“碳捕集”在 2026-02 达到季度内月度高点 44 次，随后 2026-03 回落至 38 次。</t>
+          <t>“碳移除”连续三个月保持第一，分别为 124、126、109 次，说明移除相关议题仍是季度主线。</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -1175,7 +1401,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>来源类别上，“碳移除”相关新闻 170 条，“碳捕集”相关新闻 143 条，前者略高。</t>
+          <t>“碳捕集”在 2026-02 达到季度内月度高点 44 次，随后 2026-03 回落至 38 次。</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -1183,25 +1409,25 @@
       <c r="D16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>碳移除细分技术中，“生物质”提及 46 次居首，“直接空气捕集”和“矿化”分别为 30 次和 29 次。</t>
+        </is>
+      </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>三、月度走势</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-01：92 篇，作为基准月。</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>三、月度走势</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -1211,7 +1437,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-02：96 篇，较 1 月变动 +4 篇。</t>
+          <t>2026-01：92 篇，作为基准月。</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -1221,7 +1447,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-03：90 篇，较 2 月变动 -6 篇。</t>
+          <t>2026-02：96 篇，较 1 月变动 +4 篇。</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -1229,17 +1455,17 @@
       <c r="D21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-03：90 篇，较 2 月变动 -6 篇。</t>
+        </is>
+      </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>各月前三标签：</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
@@ -1247,7 +1473,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-01：碳移除 55 次，碳捕集 40 次，碳封存 18 次</t>
+          <t>各月四大类排序：</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -1257,7 +1483,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-02：碳移除 56 次，碳捕集 44 次，碳封存 28 次</t>
+          <t>2026-01：碳移除 124 次，碳捕集 40 次，碳封存 18 次，碳利用 9 次</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
@@ -1267,7 +1493,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-03：碳移除 58 次，碳捕集 38 次，生物质 15 次</t>
+          <t>2026-02：碳移除 126 次，碳捕集 44 次，碳封存 28 次，碳利用 10 次</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -1275,25 +1501,25 @@
       <c r="D26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-03：碳移除 109 次，碳捕集 38 次，碳封存 14 次，碳利用 3 次</t>
+        </is>
+      </c>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>四、简要判断</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>从季度节奏看，新闻总量没有剧烈波动，说明 CCUS 议题保持持续曝光，而非由单一事件驱动。</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>四、简要判断</t>
         </is>
       </c>
       <c r="B29" s="2" t="n"/>
@@ -1303,7 +1529,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>从结构看，“碳移除”与“碳捕集”形成双核心，其中移除相关话题更稳定，捕集相关话题更容易受项目签约、融资或政策节点影响。</t>
+          <t>四大类口径下，季度关注度明显向碳移除集中，说明媒体仍主要围绕负排放、碳移除项目和相关技术商业化进展展开报道。</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
@@ -1313,15 +1539,25 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>“碳市场”“政策”“碳利用”等标签占比次一级，说明产业化与制度建设议题已形成辅助支撑，但尚未超过技术与项目本体的关注度。</t>
+          <t>碳捕集和碳封存在项目签约、工程建设和基础设施议题上保持稳定存在，但总量明显低于碳移除，反映产业链关注点仍偏前端技术和新项目动态。</t>
         </is>
       </c>
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>在碳移除内部，生物质、直接空气捕集和矿化形成第一梯队，森林碳汇、农业碳汇、海洋碳汇和 BECCS 构成第二梯队，显示技术路线分布较广，但热度仍向工程化程度更高的方向集中。</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
@@ -1351,6 +1587,7 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A32:D32"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1363,11 +1600,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
@@ -1375,12 +1612,12 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>英文标签</t>
+          <t>分类</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>中文标签</t>
+          <t>对应标签</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
@@ -1397,235 +1634,73 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Removal</t>
+          <t>碳移除</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>碳移除</t>
+          <t>Removal|BECCS|Ocean|Farming|Forests|Mineralization|Direct Air Capture|Biomass</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>169</v>
+        <v>359</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.2686804451510334</v>
+        <v>0.6376554174067496</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>Capture</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>122</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.1939586645468998</v>
+        <v>0.216696269982238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>碳封存</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>Storage</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>碳封存</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>60</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.09538950715421304</v>
+        <v>0.1065719360568384</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Biomass</t>
+          <t>碳利用</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>生物质</t>
+          <t>Utilization</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.07313195548489666</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Markets</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>碳市场</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0.06041335453100159</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Direct Air Capture</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>直接空气捕集</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0.04769475357710652</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Mineralization</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>矿化</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>0.04610492845786963</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>政策</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>0.04451510333863275</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Forests</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>森林碳汇</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>0.04133545310015898</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Farming</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>农业碳汇</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>0.03497615262321144</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Utilization</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>碳利用</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>0.03497615262321144</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>BECCS</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>生物质能碳捕集与封存</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>0.03179650238473768</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Ocean</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>海洋碳汇</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.03907637655417407</v>
       </c>
     </row>
   </sheetData>
@@ -1640,476 +1715,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>月份</t>
+          <t>技术方向</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>新闻数量</t>
+          <t>对应标签</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>前三标签摘要</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
+          <t>提及次数</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>碳移除 55 次，碳捕集 40 次，碳封存 18 次</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+          <t>生物质</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Biomass</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0.2421052631578947</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>碳移除 56 次，碳捕集 44 次，碳封存 28 次</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
+          <t>直接空气捕集</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Direct Air Capture</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0.1578947368421053</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>碳移除 58 次，碳捕集 38 次，生物质 15 次</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+          <t>矿化</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Mineralization</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1526315789473684</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>森林碳汇</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Forests</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1368421052631579</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>农业碳汇</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1157894736842105</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>生物质能碳捕集与封存</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>BECCS</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1052631578947368</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>各领域月度分布数据</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>分类</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Q1合计</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>碳封存</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>生物质</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>海洋碳汇</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Ocean</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>碳市场</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>直接空气捕集</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>矿化</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>政策</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>森林碳汇</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>农业碳汇</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>碳利用</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>生物质能碳捕集与封存</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>海洋碳汇</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>17</v>
+      <c r="D8" s="5" t="n">
+        <v>0.08947368421052632</v>
       </c>
     </row>
   </sheetData>
@@ -2124,16 +1884,292 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G279"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>新闻数量</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>四大类排序摘要</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>碳移除 124 次，碳捕集 40 次，碳封存 18 次，碳利用 9 次</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>碳移除 126 次，碳捕集 44 次，碳封存 28 次，碳利用 10 次</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>碳移除 109 次，碳捕集 38 次，碳封存 14 次，碳利用 3 次</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>四大类月度分布数据</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Q1合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>碳封存</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>碳利用</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="80" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2159,17 +2195,12 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>四大类归属</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>链接</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>原始来源类别</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>中文来源类别</t>
         </is>
       </c>
     </row>
@@ -2196,17 +2227,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/symbiosis-members-google-meta-and-mckinsey-invest-in-reforestation-cdr-by-living-carbon/</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -2233,17 +2259,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/px-group-secures-key-ccs-operations-contract-on-teesside/</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -2270,17 +2291,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-ctrl-s-platform-to-serve-as-a-dac-knowledge-vault/</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -2307,17 +2323,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/canada-eases-climate-rules-in-bid-to-boost-energy-investment/</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -2344,17 +2355,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-market-milestone-climefi-structures-first-publically-announced-crcf-transaction-for-major-buyers/</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -2381,17 +2387,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/cura-partners-with-sylvera-to-monetize-low-carbon-cement-advantage/</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -2418,17 +2419,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/brazil-launches-amazon-restoration-push-with-new-concession-model-awards-first-long-term-deal-to-re-green/</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -2455,17 +2451,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/belgium-carbon-pipeline-agreement-faces-scrutiny-from-civil-society/</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -2492,17 +2483,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/arukah-issues-first-puro-earth-biochar-corcs-in-cambodia/</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -2529,17 +2515,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/holcim-romania-lands-eu-funding-for-major-carbon-capture-hub/</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -2566,17 +2547,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳利用</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/econic-and-changhua-launch-first-commercial-co2-based-polyols-plant/</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2579,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/climefi-looking-for-durable-cdr-beyond-2030-in-its-most-ambitious-procurement-to-date/</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -2640,17 +2611,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/altitude-signs-deal-with-empacar-s-a-for-over-305-000-tonnes-of-biochar-cdr/</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -2677,17 +2643,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/pension-insurance-corporation-expands-cdr-portfolio-via-cur8/</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2675,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/fluxys-c-grid-antwerp-to-build-out-co2-pipeline-network/</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -2751,17 +2707,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/first-of-its-kind-beccs-project-begins-operations-in-norway/</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -2788,17 +2739,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/climeworks-and-lithos-carbon-team-up-to-bring-verified-erw-credits-to-market/</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -2825,17 +2771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/using-seawater-and-electricity-scientists-create-a-new-carbon-negative-building-material/</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -2862,17 +2803,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/microsoft-and-liferaft-ink-the-biggest-us-biochar-deal-to-date/</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2835,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/california-bill-could-tie-data-center-growth-to-energy-storage-adoption/</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -2936,17 +2867,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳利用</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/aircapture-and-almanac-debut-beer-made-with-co2-pulled-from-air/</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -2973,17 +2899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/sequestra-locks-in-over-3m-to-advance-carbon-mineralization/</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3010,17 +2931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-analysis-shows-undisturbed-old-forests-store-dramatically-more-co2-than-managed-ones/</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3047,17 +2963,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-market-tweaks-signal-eu-response-to-mounting-energy-costs/</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -3084,17 +2995,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳封存</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/beavers-emerge-as-unlikely-allies-in-carbon-removal-new-study-finds/</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -3121,17 +3027,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-sustainable-aviation-coalition-to-invest-over-2-5m-in-greenhouse-gas-removals/</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3158,17 +3059,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/major-seismic-survey-to-assess-co2-storage-potential-in-denmark/</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -3195,17 +3091,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-business-council-launches-a-direct-storage-of-biomass-coalition/</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3232,17 +3123,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/aker-solutions-secures-feed-contract-for-baltic-co2-terminal/</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -3269,17 +3155,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-sabah-rainforest-rehabilitation-project-in-malaysia-is-now-issuing-high-quality-credits/</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3306,17 +3187,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/spiritus-taps-energy-and-tesla-experts-to-expand-carbon-negative-infrastructure/</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3343,17 +3219,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/in-a-new-study-catf-evaluates-the-strenght-of-existing-biomass-cdr-protocols/</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3380,17 +3251,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/cocoon-raises-15m-to-scale-low-carbon-cement-alternative/</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3283,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/marine-carbon-removal-gains-momentum-but-can-it-scale-responsibly/</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3454,17 +3315,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/louisiana-republicans-clash-over-carbon-capture-in-senate-race/</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -3491,17 +3347,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/looming-corsia-deadline-exposes-gaps-in-carbon-credit-supply-bezero-says/</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3528,17 +3379,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/google-purchases-200000-tons-of-biochar-cdr-from-amp/</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3565,17 +3411,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/empacar-puro-earth-cula-bioflux-unite-on-new-biochar-initiative-in-bolivia/</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3602,17 +3443,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-capture-europe-summit-everyones-talking-about-risk-and-eggs/</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -3639,17 +3475,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/verde-secures-biochar-supply-deal-to-scale-carbon-storing-products/</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3676,17 +3507,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳利用</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/rubi-secures-7-5m-and-60m-offtake-deals-to-scale-co2-to-materials-tech/</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -3713,17 +3539,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/octopus-energy-generation-bumps-up-cultivo-partnership-with-new-60m/</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3750,17 +3571,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/epa-issues-draft-class-vi-permit-for-colorado-co2-storage-project/</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -3787,17 +3603,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳移除</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/cura-and-captura-combine-technologies-in-novel-collaboration/</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -3824,17 +3635,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/when-carbon-capture-meets-the-real-world-lessons-from-scandinavia/</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -3861,17 +3667,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/sweden-to-back-negative-emissions-projects-and-research-in-two-new-calls/</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -3898,17 +3699,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/kent-wins-feed-contract-for-greeces-prinos-co2-storage-project/</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -3935,17 +3731,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/in-a-landmark-motion-the-govt-of-canada-to-invest-at-least-7m-in-cdr-credits/</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -3972,17 +3763,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/conflict-in-middle-east-casts-doubt-on-gulf-carbon-capture-buildout-rystad/</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -4009,17 +3795,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/co2next-launches-market-call-for-rail-co2-delivery-to-rotterdam-terminal/</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -4046,17 +3827,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/warm-springs-ends-25m-forest-carbon-project-after-wildfire-loss/</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4083,17 +3859,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/rewind-deep-mine-storage-cdr-bluelayer-dmrv/</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4120,17 +3891,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/frontier-launches-call-for-2026-carbon-removal-innovation-program/</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4157,17 +3923,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/eu-approves-298m-belgian-state-aid-for-kairosc-ccs-project/</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -4194,17 +3955,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/cura-and-gfc-move-to-commercialize-low-carbon-cement/</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -4231,17 +3987,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/rainforest-builder-secures-series-a-support-for-ecosystem-restoration-in-west-africa/</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4268,17 +4019,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-centrics-kirkenaer-beccs-project-successfully-advances-towards-certification/</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -4305,17 +4051,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/wirral-council-urges-uk-government-to-scrap-peak-cluster-co2-pipeline/</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -4342,17 +4083,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/svante-advances-new-beccs-project-at-us-paper-mill/</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -4379,17 +4115,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/dp-world-launches-carbon-inset-trial-to-reduce-ocean-freight-emissions/</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4416,17 +4147,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/climefi-publishes-2026-insights-on-the-durable-carbon-removal-market/</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4453,17 +4179,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/bregal-sphere-to-back-imperative-with-up-to-500m-for-nature-restoration-projects/</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4490,17 +4211,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/poet-sues-indiana-county-over-carbon-capture-moratorium/</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -4527,17 +4243,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-carbon-gap-cdr-readiness-assesment-says-spain-can-lead-in-removals-if-policy-paves-the-way-rapidly/</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4564,17 +4275,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-direct-outlines-groundbreaking-roadmap-for-pairing-superpollutants-mitigation-with-cdr/</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4601,17 +4307,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/airco-develops-containerized-mad-system-for-on-demand-synthetic-fuel/</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -4638,17 +4339,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/watershed-opens-2026-carbon-removal-rfp-round/</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4675,17 +4371,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/svitzer-unveils-coastal-co2-shipping-model-for-emerging-ccs-networks/</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4403,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-whitepaper-outlines-electrochemical-cdr-scaling-opportunities-in-mining/</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4749,17 +4435,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/biochar-leader-exomad-green-surpasses-300000-delivered-carbon-removal-credits/</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4786,17 +4467,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳移除</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/iea-carbon-management-funding-policy-support/</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -4823,17 +4499,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/sirona-technologies-secures-new-cdr-agreement-facilitated-by-patch/</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4860,17 +4531,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/saipem-and-capsol-join-forces-on-large-scale-carbon-capture-deployment/</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -4897,17 +4563,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/nep-begins-appraisal-drilling-for-uk-ccs-project/</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -4934,17 +4595,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/a-new-advance-carbon-removal-coalition-to-drive-demand-for-canadian-cdr/</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -4971,17 +4627,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/syzygy-expands-global-saf-pipeline-with-new-brazil-biogas-agreement/</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -5008,17 +4659,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/svante-acquires-canada-based-cdr-developer-carbon-alpha/</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -5045,17 +4691,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/strategic-biofuels-ccs-project-receives-draft-class-vi-well-permit/</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -5082,17 +4723,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳移除</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-management-society-opens-membership-as-climate-accountability-tightens/</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -5119,17 +4755,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/boeing-inks-a-new-deal-with-carbonfuture-for-one-of-aviations-boldest-cdr-procurements/</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5156,17 +4787,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-mercedes-amg-petronas-f1-team-expands-its-global-cdr-portfolio/</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5193,17 +4819,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/smi-urges-dedicated-fund-to-close-ccs-financing-gap/</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -5230,17 +4851,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳封存</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/octavia-carbon-secures-an-offtake-agreement-via-carbon-direct/</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -5267,17 +4883,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/greece-grants-25-year-co2-storage-permit-for-prinos-project/</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -5304,17 +4915,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-startup-cur8-taps-fintech-executive-as-coo-to-drive-next-phase-of-growth/</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5341,17 +4947,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/airmyne-eneos-direct-air-capture/</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5378,17 +4979,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-carbon-business-council-emerald-climate-back-removals-in-asia-pacific-with-new-apacdr-initiative/</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5415,17 +5011,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/seabound-deploys-first-full-scale-onboard-ccs-system/</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -5452,17 +5043,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/cur8-secures-new-strategic-investment-from-tokyo-gas-backed-acario/</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5489,17 +5075,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/45q-tax-credit-faces-growing-backlash-over-oil-linked-carbon-capture/</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -5526,17 +5107,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-lego-group-invests-new-2-8m-in-cdr-projects/</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5563,17 +5139,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/supercritical-transacts-the-largest-volumes-of-puro-earth-delivered-cdr-credits-for-a-second-year-in-a-row/</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5600,17 +5171,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/ccsa-warns-ccus-delays-eu/</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -5637,17 +5203,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/air-liquide-and-holcim-to-decarbonize-cement-with-carbon-capture-in-belgium/</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -5674,17 +5235,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/u-s-congress-now-considering-first-mcdr-research-bill/</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5711,17 +5267,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/lithuanias-akmenes-cementas-lines-up-e700m-carbon-capture-bet/</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -5748,17 +5299,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/indigo-ag-tops-2m-metric-tons-of-verified-soil-carbon-credits/</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5785,17 +5331,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-direct-partners-with-c2x-on-a-biomass-to-biofuel-project-in-louisiana/</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5822,17 +5363,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/verified-soil-carbon-credits-deliver-new-income-stream-for-u-s-farmers/</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5859,17 +5395,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-us-nist-carbon-removal-consortium-welcomes-avantium-as-a-new-member/</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -5896,17 +5427,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/soderenergi-freezes-carbon-capture-plans-amid-market-uncertainty/</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -5933,17 +5459,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/stanlow-consortium-maps-co2-shipping-route-into-uk-offshore-storage/</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -5970,17 +5491,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/climeworks-and-rcjy-strenghten-partnership-to-advance-large-scale-dac-in-saudi-arabia/</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6007,17 +5523,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/sweden-backs-malmo-co2-hub-to-anchor-emerging-ccs-network/</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -6044,17 +5555,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/in-a-new-deal-microsoft-buys-forest-restoration-credits-from-rainforest-builder/</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6081,17 +5587,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/grassroots-carbon-is-now-a-member-of-the-soil-carbon-consortium-at-colorado-state-university/</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6118,17 +5619,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-study-determines-the-best-us-spots-for-electrochemical-mcdr-deployments/</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6155,17 +5651,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/louisiana-regulator-pushes-back-on-ngo-report-criticizing-ccs-oversight/</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -6192,17 +5683,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/climeworks-announces-new-headquarters-in-alberta-canada/</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6229,17 +5715,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/canada-launches-new-ccus-feed-funding-call-to-accelerate-investment-ready-projects/</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -6266,17 +5747,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/lapis-carbon-solutions-files-class-vi-permit-for-ccs-project-in-illinois/</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -6303,17 +5779,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳移除|碳封存</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/irs-creates-temporary-safe-harbor-to-shield-45q-carbon-capture-credits/</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -6340,17 +5811,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/fls-group-and-cula-join-forces-to-tackle-a-conflict-of-interest-in-biochar-mrv/</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6377,17 +5843,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/climate-impact-partners-registers-the-first-vm0047-project-in-india/</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6414,17 +5875,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-direct-releases-new-cdr-2-0-framework-for-moving-the-needle-from-commitment-to-delivery/</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6451,17 +5907,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/varaha-introduces-new-biochar-partnership-program-kicking-off-novel-project-in-cote-divoire/</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6488,17 +5939,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/senken-enriches-its-portfolio-of-cdr-offerings-with-european-forestry-credits-by-ocell/</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6525,17 +5971,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-abb-ccus-measurement-system-targets-pipeline-safety-and-co2-quality/</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -6562,17 +6003,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/exxonmobil-starts-up-second-ccs-project-in-louisiana-with-ng3-launch/</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -6599,17 +6035,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/climefi-launches-its-new-due-diligence-coverage-platform-easing-buyers-with-cdr-decisions/</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6636,17 +6067,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-u-s-environmental-protection-agency-grants-14-7m-for-a-biochar-project-by-the-tule-river-tribe/</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6673,17 +6099,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-colorado-energy-office-awards-2-35m-to-crew-carbon-and-its-wastewater-treatment-cdr-tech/</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6710,17 +6131,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳封存</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/tapestry-invests-in-the-most-diversified-cdr-portfolio-by-climeworks-to-date/</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -6747,17 +6163,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/senate-democrats-challenge-doe-over-ccus-funds-redirected-to-coal/</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -6784,17 +6195,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/malaysia-and-japan-advance-cross-border-ccs-plan/</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -6821,17 +6227,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbonquest-enters-canada-with-mof-enhanced-ccs/</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -6858,17 +6259,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/uks-octopus-energy-invests-1b-in-cdr-and-clean-energy-tech-in-california/</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6895,17 +6291,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-alliedoffsets-research-notes-a-maturing-cdr-market-paired-with-exits-consolidations-strategic-partnerships/</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -6932,17 +6323,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/mhi-advances-integrated-pathway-for-synthetic-aviation-fuel-from-co2/</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -6969,17 +6355,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/cascade-climate-is-looking-for-partners-for-a-new-coordinated-erw-research-network/</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7006,17 +6387,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/skynrg-advances-first-dutch-saf-plant-into-construction-phase/</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7043,17 +6419,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/releaf-earth-issues-first-carbon-credits-for-salesforce-via-milkywire/</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7080,17 +6451,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳封存</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/in-a-new-partnership-mangrove-systems-to-provide-dmrv-for-super6s-u-s-based-cdr-network/</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -7117,17 +6483,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/alberta-funds-integrated-rng-and-carbon-capture-project-in-coaldale/</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7154,17 +6515,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳封存</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/rothschild-co-to-invest-in-accelerated-carbonation-credits-by-o-c-o-technology/</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -7191,17 +6547,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/france-commits-2b-to-industrial-decarbonization-ccus/</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7228,17 +6579,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/eu-funding-supports-co2-terminal-development-in-hirtshals/</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7265,17 +6611,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳移除</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/curbing-ghg-pollution-is-no-longer-a-u-s-federal-responsibility-and-carbon-removal-and-capture-now-face-new-uncertainties/</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -7302,17 +6643,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbogenics-to-scale-biochar-operations-with-new-3m-funding/</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7339,17 +6675,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/worley-selected-for-engineering-work-on-qatar-lng-co2-storage-project/</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7376,17 +6707,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/introducing-a-new-cdr-messaging-and-lexicon-guide-by-the-carbon-business-council-and-potential-energy-coalition/</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7413,17 +6739,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/goodcarbon-is-looking-for-nature-based-cdr-credits-for-a-food-beverage-company/</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7450,17 +6771,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/global-ccs-institute-opens-submissions-for-2026-tech-showcase/</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7487,17 +6803,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/exomad-green-partners-with-senken-on-new-cdr-deal-indended-for-the-aviation-industry/</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7524,17 +6835,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-supercritical-report-examines-how-delivery-risk-is-reshaping-the-cdr-demand/</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7561,17 +6867,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/dnv-endorses-adnoc-west-aquifer-co2-storage-site/</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7598,17 +6899,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/chestnuts-forestry-project-is-now-the-first-such-u-s-fsc-verified-initiative-for-biodiversity-conservation-impact/</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7635,17 +6931,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/opinion-cross-border-carbon-storage-the-other-exchange-programme/</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7672,17 +6963,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/is-balancing-short-term-and-durable-carbon-removals-the-key-to-reaching-climate-targets/</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7709,17 +6995,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/exclusive-carbon-directs-2026-state-of-vcm-report-highlights-buyer-hesitancy-as-a-bottleneck-for-cdr-scale-up/</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7746,17 +7027,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/equinor-steps-back-from-ccs-expansion-as-market-signals-weaken/</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7783,17 +7059,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/denmarks-ccs-tender-failure-or-reality-check/</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7820,17 +7091,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon180-the-carbon-business-council-ocean-concervancy-launch-new-mcdr-forum/</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7857,17 +7123,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/quebec-tables-bill-17-to-regulate-geological-co2-storage/</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7894,17 +7155,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/prinos-co2-storage-project-offshore-greece-gets-eu-endorsement/</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -7931,17 +7187,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/parallel-carbon-to-deliver-cdr-for-zurich-insurance-group-via-novel-dach2-technology/</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -7968,17 +7219,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-oxford-study-signals-legal-risks-in-cdr-overreliance/</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -8005,17 +7251,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbonstorage-io-launches-global-ccs-and-low-carbon-infrastructure-intelligence-platform/</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -8042,17 +7283,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/boomitra-issues-an-eyecatching-3-03m-credits-from-the-largest-verra-approved-soil-carbon-project-to-date/</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -8079,17 +7315,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳利用</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-removal-and-utilization-get-a-boost-earthshot-and-bezos-earth-fund-back-next-gen-climate-firms/</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -8116,17 +7347,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/uk-opens-new-route-for-ccus-projects-to-join-east-coast-cluster-teesside/</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -8153,17 +7379,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/terradot-acquires-eion-forming-new-leading-enhanced-rock-weathering-platform/</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -8190,17 +7411,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/germany-can-unlock-net-zero-by-2045-if-cdr-is-scaled-rapidly-says-new-carbon-gap-sweco-report/</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -8227,17 +7443,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/dutch-porthos-project-prepares-north-sea-gas-wells-for-co2-injection/</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -8264,17 +7475,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/climate-startup-phathom-secures-over-12m-to-advance-coastal-carbon-capture-technology/</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -8301,17 +7507,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/ontario-opens-door-to-new-commercial-carbon-storage-projects/</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -8338,17 +7539,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-study-finds-removing-livestock-from-grasslands-may-compromise-soil-carbon-sinks/</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -8375,17 +7571,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-mexico-moves-to-slash-carbon-sequestration-approval-times/</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -8412,17 +7603,12 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/climeworks-embarks-on-a-muli-year-agreement-with-biochar-company-truecoco/</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -8449,17 +7635,12 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/clean-hydrogen-works-takes-exxonmobil-to-court-over-co2-pipeline-access/</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -8486,17 +7667,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/varaha-secures-20m-to-scale-carbon-removal-in-the-global-south/</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -8523,17 +7699,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/us-treasury-and-irs-unveil-draft-rules-for-clean-fuel-tax-credit/</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -8560,17 +7731,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/marsh-report-flags-policy-gaps-that-could-undermine-european-ccs-funding/</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -8597,17 +7763,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳封存</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/eu-adopts-the-worlds-first-voluntary-standard-for-permanent-cdr/</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -8634,17 +7795,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/aalborg-portland-targets-1-4-mt-co2-capture-with-bid-for-denmarks-ccs-funding-pool/</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -8671,17 +7827,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/oxyfuel-combustion-seen-as-fast-track-decarbonization-tool-for-heavy-industry/</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -8708,17 +7859,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/cloverly-to-help-streamline-carbon-transactions-for-dutch-company-scature/</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -8745,17 +7891,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/climate-impact-partners-apponts-ryan-king-as-its-new-chief-growth-officer/</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -8782,17 +7923,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/verra-applies-first-corsia-labels-to-voluntary-carbon-credits-from-africa/</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -8819,17 +7955,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/sweden-opens-new-28m-bio-ccs-funding-call-under-industriklivet/</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G181" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -8856,17 +7987,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/siemens-to-help-ucaneo-optimize-operations-at-its-dac-plants/</t>
-        </is>
-      </c>
-      <c r="F182" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G182" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -8893,17 +8019,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/northern-lights-orders-four-more-co2-ships/</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G183" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -8930,17 +8051,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/ghg-protocol-rolls-out-first-global-standard-for-land-sector-emissions-and-carbon-removal/</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -8967,17 +8083,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/fls-group-and-decarboengineering-team-up-on-biochar-deployment-in-paraguay/</t>
-        </is>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -9004,17 +8115,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/did-carbon-actually-score-a-quiet-win-in-congress/</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -9041,17 +8147,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/india-puts-2-4-billion-behind-carbon-capture-push-in-next-budget/</t>
-        </is>
-      </c>
-      <c r="F187" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G187" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9078,17 +8179,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-miombo-restoration-alliance-backed-by-trafigura-to-invest-over-1b-in-four-cdr-projects/</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -9115,17 +8211,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳封存</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/mast-reforestation-sells-and-delivers-first-credits-from-its-biomass-burial-and-post-fire-restoration-project/</t>
-        </is>
-      </c>
-      <c r="F189" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G189" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -9152,17 +8243,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/drax-rolls-out-digital-biomass-tracker-to-increase-supply-chain-transparency/</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9189,17 +8275,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/uk-sweden-alliance-targets-baltic-sea-ccus-infrastructure-build-out/</t>
-        </is>
-      </c>
-      <c r="F191" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9226,17 +8307,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/slb-records-major-loss-linked-to-carbon-capture-project/</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9263,17 +8339,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳利用</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/co-reactive-secures-more-than-7m-in-seed-funding-for-its-cement-decarbonization-solution/</t>
-        </is>
-      </c>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G193" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -9300,17 +8371,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbonaide-to-scale-its-carbon-negative-concrete-tech-with-new-4-4m-funding/</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G194" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -9337,17 +8403,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳封存</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/wild-assets-invests-in-deep-mine-storage-credits-by-rewind/</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -9374,17 +8435,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳利用</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/u-s-saf-market-consolidates-as-xcf-global-southern-energy-and-devvstream-discuss-joining-forces/</t>
-        </is>
-      </c>
-      <c r="F196" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G196" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9411,17 +8467,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/puro-earth-unveils-premium-service-to-accelerate-carbon-credit-issuance/</t>
-        </is>
-      </c>
-      <c r="F197" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G197" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -9448,17 +8499,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳利用</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/lanzatech-secures-20m-funding-to-advance-carbon-utilization-deployment/</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9485,17 +8531,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/in-a-new-analysis-canada-energy-regulator-reflects-on-the-countrys-growing-cdr-sector/</t>
-        </is>
-      </c>
-      <c r="F199" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G199" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -9522,17 +8563,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/holcim-deepens-carbon-capture-strategy-with-capsol-investment/</t>
-        </is>
-      </c>
-      <c r="F200" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9559,17 +8595,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/orphan-wells-industry-software-well-done-foundation/</t>
-        </is>
-      </c>
-      <c r="F201" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9596,17 +8627,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/exxon-launches-commercial-ccs-operations-with-cf-industries-in-louisiana/</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9633,17 +8659,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/uk-and-eu-port-operators-launch-carbon-shipping-collaboration/</t>
-        </is>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G203" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9670,17 +8691,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/origen-successfully-demonstrates-its-pioneering-zero-emissions-lime-kiln-in-north-dakota/</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -9707,17 +8723,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/indiana-advances-bid-to-regulate-carbon-storage-wells/</t>
-        </is>
-      </c>
-      <c r="F205" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9744,17 +8755,12 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/ceezer-and-swisscom-team-up-to-expand-cdr-access-and-scale-deployments/</t>
-        </is>
-      </c>
-      <c r="F206" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -9781,17 +8787,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-negative-emissions-platform-outlines-ways-to-unlock-short-term-cdr-demand-in-the-eu/</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G207" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -9818,17 +8819,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/south-africa-issues-first-verra-ccb-labeled-grassland-carbon-credits-globally/</t>
-        </is>
-      </c>
-      <c r="F208" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G208" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -9855,17 +8851,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/eu-is-now-looking-for-input-on-the-crcf-regulation/</t>
-        </is>
-      </c>
-      <c r="F209" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G209" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -9892,17 +8883,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/ccus-set-to-play-minor-role-in-net-zero-transition-ieefa-says/</t>
-        </is>
-      </c>
-      <c r="F210" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G210" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9929,17 +8915,12 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/ais-climate-impact-can-carbon-capture-solve-data-center-emissions/</t>
-        </is>
-      </c>
-      <c r="F211" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G211" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -9966,17 +8947,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/iowa-house-moves-to-ban-eminent-domain-for-carbon-pipelines/</t>
-        </is>
-      </c>
-      <c r="F212" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G212" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -10003,17 +8979,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/gold-standard-releases-new-methodology-for-cdr-through-microbial-co2-mineralization/</t>
-        </is>
-      </c>
-      <c r="F213" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G213" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10040,17 +9011,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/gevo-north-dakota-facility-issues-500000-high-integrity-carbon-removal-credits/</t>
-        </is>
-      </c>
-      <c r="F214" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G214" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10077,17 +9043,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/frontier-buyers-back-two-companies-working-on-innovative-zero-carbon-lime/</t>
-        </is>
-      </c>
-      <c r="F215" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G215" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10114,17 +9075,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/kapture-partners-with-vinci-to-accelerate-global-carbon-capture-deployment/</t>
-        </is>
-      </c>
-      <c r="F216" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -10151,17 +9107,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/first-uk-offshore-ccs-project-moves-to-construction/</t>
-        </is>
-      </c>
-      <c r="F217" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G217" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -10188,17 +9139,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/dnv-strikes-a-long-term-cdr-agreement-with-carbon-centric/</t>
-        </is>
-      </c>
-      <c r="F218" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G218" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -10225,17 +9171,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/charm-industrial-eyes-canadian-market-after-inking-a-new-cdr-deal-with-td-bank/</t>
-        </is>
-      </c>
-      <c r="F219" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G219" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10262,17 +9203,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/belgian-wastewater-treatment-expert-aquafin-to-develop-a-biochar-project/</t>
-        </is>
-      </c>
-      <c r="F220" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G220" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10299,17 +9235,12 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-inlandsis-fund-invests-in-peatland-cdr-credits-from-pantheon-regeneration/</t>
-        </is>
-      </c>
-      <c r="F221" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G221" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10336,17 +9267,12 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/japans-mitsui-o-s-k-lines-unveils-first-tangible-carbon-removals-under-environmental-vision/</t>
-        </is>
-      </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10373,17 +9299,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/inpex-pulls-bonaparte-ccs-project-from-federal-review/</t>
-        </is>
-      </c>
-      <c r="F223" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G223" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -10410,17 +9331,12 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbonrun-issues-worlds-first-river-alkalinity-enhancement-credits/</t>
-        </is>
-      </c>
-      <c r="F224" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G224" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10447,17 +9363,12 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/wakefield-biochar-now-issuing-puro-earth-certified-credist-from-a-new-georgia-facility/</t>
-        </is>
-      </c>
-      <c r="F225" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G225" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10484,17 +9395,12 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/syzygy-plasmonics-and-trafigura-sign-long-term-saf-offtake-agreement/</t>
-        </is>
-      </c>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -10521,17 +9427,12 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/nuada-and-mlc-to-demonstrate-next-gen-carbon-capture-at-uk-lime-facility/</t>
-        </is>
-      </c>
-      <c r="F227" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -10558,17 +9459,12 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/in-2026-avnos-predicts-a-strong-hybrid-dac-demand-driven-by-ai-data-centers-and-industrial-decarbonization/</t>
-        </is>
-      </c>
-      <c r="F228" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10595,17 +9491,12 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/switzerland-advances-co2-transport-plans-with-penspen-pipeline-study/</t>
-        </is>
-      </c>
-      <c r="F229" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G229" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -10632,17 +9523,12 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-whitepaper-outlines-major-cdr-scaling-opportunities-via-industrial-mineralization/</t>
-        </is>
-      </c>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10669,17 +9555,12 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳移除</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/netherlands-bets-%d0%ben-carbon-removal-with-new-11-5m-innovation-push/</t>
-        </is>
-      </c>
-      <c r="F231" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G231" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -10706,17 +9587,12 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/is-2026-going-to-be-a-breakthrough-year-for-cdr/</t>
-        </is>
-      </c>
-      <c r="F232" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G232" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10743,17 +9619,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/gevo-appoints-alex-clayton-as-chief-carbon-officer/</t>
-        </is>
-      </c>
-      <c r="F233" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G233" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -10780,17 +9651,12 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbonsate-marks-first-credit-issuance-from-its-puro-earth-certified-biomass-storage-project/</t>
-        </is>
-      </c>
-      <c r="F234" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G234" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10817,17 +9683,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/totalenergies-mitsui-and-nordsofonden-secure-new-co2-storage-exploration-permit/</t>
-        </is>
-      </c>
-      <c r="F235" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G235" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -10854,17 +9715,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/neg8-prochem-partner-on-an-engineering-study-for-a-new-dac-project-in-ireland/</t>
-        </is>
-      </c>
-      <c r="F236" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G236" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10891,17 +9747,12 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/arca-giga-metals-to-explore-cdr-at-nickel-mine-in-canada/</t>
-        </is>
-      </c>
-      <c r="F237" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G237" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -10928,17 +9779,12 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/abu-dhabi-launches-carbon-capture-policy-to-strengthen-ccus-framework/</t>
-        </is>
-      </c>
-      <c r="F238" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -10965,17 +9811,12 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/serbia-prepares-legal-framework-for-geological-co2-storage/</t>
-        </is>
-      </c>
-      <c r="F239" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G239" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -11002,17 +9843,12 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/microsoft-continues-its-cdr-purchase-streak-with-new-deal-signed-with-varaha/</t>
-        </is>
-      </c>
-      <c r="F240" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G240" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11039,17 +9875,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/microsoft-buys-new-2-85m-credits-from-indigo-ag-in-one-of-the-largest-soil-cdr-deals-to-date/</t>
-        </is>
-      </c>
-      <c r="F241" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G241" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11076,17 +9907,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/iowa-house-committee-advances-eminent-domain-ban-for-co2-pipelines/</t>
-        </is>
-      </c>
-      <c r="F242" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G242" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -11113,17 +9939,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存|碳利用</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/whats-next-for-carbon-capture-utilization-storage-ccus-in-2026/</t>
-        </is>
-      </c>
-      <c r="F243" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G243" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -11150,17 +9971,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/toray-trial-shows-70-cost-reduction-in-biogas-co2-separation/</t>
-        </is>
-      </c>
-      <c r="F244" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G244" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -11187,17 +10003,12 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/rubicon-carbon-to-provide-microsoft-with-2m-forestry-credits-from-ugandan-kijani-project/</t>
-        </is>
-      </c>
-      <c r="F245" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G245" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11224,17 +10035,12 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/cella-and-pronoe-secure-prepurchase-deals-with-frontier-buyers/</t>
-        </is>
-      </c>
-      <c r="F246" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G246" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11261,17 +10067,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/us-supreme-court-rejects-iowa-counties-bid-to-regulate-carbon-pipeline/</t>
-        </is>
-      </c>
-      <c r="F247" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G247" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -11298,17 +10099,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/petrobras-shell-team-up-to-fund-carbon-stock-study-across-brazil/</t>
-        </is>
-      </c>
-      <c r="F248" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G248" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11335,17 +10131,12 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/milkywire-launches-a-2026-open-call-for-durable-carbon-removal/</t>
-        </is>
-      </c>
-      <c r="F249" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G249" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11372,17 +10163,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/louisiana-lawmaker-proposes-bills-to-regulate-carbon-capture-projects/</t>
-        </is>
-      </c>
-      <c r="F250" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G250" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -11409,17 +10195,12 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/blusky-associated-energy-developers-ink-8-3m-deal-to-expand-the-ar1-biochar-site/</t>
-        </is>
-      </c>
-      <c r="F251" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G251" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11446,17 +10227,12 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/bain-company-joins-growing-list-of-1pointfives-direct-air-capture-buyers/</t>
-        </is>
-      </c>
-      <c r="F252" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G252" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11483,17 +10259,12 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/uk-pushes-carbon-removal-forward-with-publication-of-final-innovation-reports/</t>
-        </is>
-      </c>
-      <c r="F253" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G253" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -11520,17 +10291,12 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-cdr-fyi-report-shows-the-flow-of-carbon-removal-investments-in-the-past-5-years/</t>
-        </is>
-      </c>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11557,17 +10323,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/gcmd-study-finds-emissions-savings-across-onboard-carbon-capture-value-chain/</t>
-        </is>
-      </c>
-      <c r="F255" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G255" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -11594,17 +10355,12 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/exomad-green-starts-2026-with-new-capacity-at-riberalta-site/</t>
-        </is>
-      </c>
-      <c r="F256" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G256" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11631,17 +10387,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/alabama-watershed-authority-supports-legislation-to-block-co2-storage-project/</t>
-        </is>
-      </c>
-      <c r="F257" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G257" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -11668,17 +10419,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/salesforce-and-milkywire-ignite-investment-in-emerging-carbon-removal-technologies/</t>
-        </is>
-      </c>
-      <c r="F258" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G258" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11705,17 +10451,12 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/greentown-labs-shell-technip-energies-launch-new-climate-tech-innovation-program/</t>
-        </is>
-      </c>
-      <c r="F259" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G259" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11742,17 +10483,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/grassroots-carbon-delivers-1-9-mt-of-removals-through-regenerative-ranching/</t>
-        </is>
-      </c>
-      <c r="F260" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G260" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11779,17 +10515,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/equitable-earth-to-accelerate-nature-based-cdr-certification-with-new-14-6m-funding/</t>
-        </is>
-      </c>
-      <c r="F261" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G261" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11816,17 +10547,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/foxconn-looking-to-solve-one-carbon-transportationss-biggest-challenges/</t>
-        </is>
-      </c>
-      <c r="F262" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G262" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -11853,17 +10579,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/chevrons-gorgon-ccs-project-posts-lowest-carbon-storage-levels-on-record/</t>
-        </is>
-      </c>
-      <c r="F263" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G263" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -11890,17 +10611,12 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/ceezer-is-looking-to-back-nature-based-cdr-in-its-fourth-accelerator-program/</t>
-        </is>
-      </c>
-      <c r="F264" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G264" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -11927,17 +10643,12 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-centric-receives-9m-enova-grant-for-its-new-skogn-project/</t>
-        </is>
-      </c>
-      <c r="F265" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G265" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -11964,17 +10675,12 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳封存</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/the-carbon-removers-locks-in-nearly-1-3-million-in-support-from-sose/</t>
-        </is>
-      </c>
-      <c r="F266" s="2" t="inlineStr">
-        <is>
-          <t>capture|removal</t>
-        </is>
-      </c>
-      <c r="G266" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集|碳移除</t>
         </is>
       </c>
     </row>
@@ -12001,17 +10707,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
+          <t>碳移除|碳捕集|碳封存</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/swiss-beccs-project-secures-cross-border-co2-storage-deal/</t>
-        </is>
-      </c>
-      <c r="F267" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G267" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -12038,17 +10739,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/new-study-links-microplastics-to-reduced-ocean-carbon-absorption/</t>
-        </is>
-      </c>
-      <c r="F268" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G268" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -12075,17 +10771,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/2025-alliedoffsets-review-notes-vcm-growth-in-a-concentrated-manner/</t>
-        </is>
-      </c>
-      <c r="F269" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G269" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -12112,17 +10803,12 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/stack-carbon-to-develop-the-first-large-scale-biochar-facility-in-uganda/</t>
-        </is>
-      </c>
-      <c r="F270" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G270" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -12149,17 +10835,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/decatur-to-host-community-forum-amid-carbon-capture-concerns/</t>
-        </is>
-      </c>
-      <c r="F271" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G271" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -12186,17 +10867,12 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbonfuture-secures-an-investment-from-idemitsu-americas-holdings-corporation/</t>
-        </is>
-      </c>
-      <c r="F272" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G272" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -12223,17 +10899,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/babcock-wilcox-moves-forward-on-solvebright-carbon-capture-deployment/</t>
-        </is>
-      </c>
-      <c r="F273" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G273" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -12260,17 +10931,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
+          <t>碳捕集|碳利用</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/aramcos-lab7-invests-in-u-s-co2-to-graphite-startup-homeostasis/</t>
-        </is>
-      </c>
-      <c r="F274" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G274" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -12297,17 +10963,12 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/ongc-launches-first-ccs-pilot-at-gujarats-gandhar-oilfield/</t>
-        </is>
-      </c>
-      <c r="F275" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G275" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -12334,17 +10995,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/eneos-sumitomo-and-44-01-partner-on-new-carbon-mineralization-demonstration/</t>
-        </is>
-      </c>
-      <c r="F276" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G276" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -12371,17 +11027,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
+          <t>碳捕集</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carbon-pipeline-issue-expected-to-shape-iowa-2026-legislative-agenda/</t>
-        </is>
-      </c>
-      <c r="F277" s="2" t="inlineStr">
-        <is>
-          <t>capture</t>
-        </is>
-      </c>
-      <c r="G277" s="2" t="inlineStr">
-        <is>
-          <t>碳捕集</t>
         </is>
       </c>
     </row>
@@ -12408,17 +11059,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/carba-inaugurates-innovative-molten-salt-pyrolysis-reactor/</t>
-        </is>
-      </c>
-      <c r="F278" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G278" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
@@ -12445,17 +11091,12 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
+          <t>碳移除</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
           <t>https://carbonherald.com/can-massachusetts-turn-power-hungry-data-centers-into-carbon-removal-engines/</t>
-        </is>
-      </c>
-      <c r="F279" s="2" t="inlineStr">
-        <is>
-          <t>removal</t>
-        </is>
-      </c>
-      <c r="G279" s="2" t="inlineStr">
-        <is>
-          <t>碳移除</t>
         </is>
       </c>
     </row>
